--- a/resources/templates/standard/L1200-06.xlsx
+++ b/resources/templates/standard/L1200-06.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>NO</t>
   </si>
@@ -680,7 +683,9 @@
   </cols>
   <sheetData>
     <row r="1" ht="35.1" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -735,24 +740,24 @@
     </row>
     <row r="4" ht="27" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
@@ -774,7 +779,7 @@
       <c r="F5" s="6"/>
       <c r="G5" s="7"/>
       <c r="H5" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
@@ -865,35 +870,35 @@
     </row>
     <row r="10" ht="19.5" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
       <c r="D10" s="14"/>
       <c r="E10" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I10" s="16" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J10" s="16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K10" s="16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L10" s="14"/>
       <c r="M10" s="16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N10" s="16"/>
       <c r="O10" s="16"/>
@@ -915,16 +920,16 @@
       <c r="K11" s="17"/>
       <c r="L11" s="14"/>
       <c r="M11" s="19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P11" s="20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" ht="23.25" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
